--- a/release_notes/PARAM/PARAM_17.3_vs_17.2.xlsx
+++ b/release_notes/PARAM/PARAM_17.3_vs_17.2.xlsx
@@ -1589,7 +1589,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RF-00012847-PAR</t>
+          <t>RF-00013297-PAR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RF-00013297-PAR</t>
+          <t>RF-00013302-PAR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RF-00013302-PAR</t>
+          <t>RF-00013765-PAR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RF-00013765-PAR</t>
+          <t>RF-00014167-PAR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RF-00014167-PAR</t>
+          <t>RF-00014482-PAR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RF-00014482-PAR</t>
+          <t>RF-00015022-PAR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1697,7 +1697,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RF-00014917-PAR</t>
+          <t>RF-00015093-PAR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RF-00015022-PAR</t>
+          <t>RF-00015159-PAR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RF-00015093-PAR</t>
+          <t>RF-00016207-PAR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RF-00015159-PAR</t>
+          <t>RF-00012281-PAR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RF-00016207-PAR</t>
+          <t>RF-00012682-PAR</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1787,7 +1787,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RF-00012281-PAR</t>
+          <t>RF-00012727-PAR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RF-00012682-PAR</t>
+          <t>RF-00012771-PAR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RF-00012727-PAR</t>
+          <t>RF-00012847-PAR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RF-00012771-PAR</t>
+          <t>RF-00012852-PAR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RF-00012852-PAR</t>
+          <t>RF-00013061-PAR</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1877,7 +1877,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RF-00013061-PAR</t>
+          <t>RF-00013159-PAR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RF-00013159-PAR</t>
+          <t>RF-00014490-PAR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1913,7 +1913,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RF-00013161-PAR</t>
+          <t>RF-00014561-PAR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RF-00014490-PAR</t>
+          <t>RF-00014586-PAR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RF-00014561-PAR</t>
+          <t>RF-00014917-PAR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RF-00014586-PAR</t>
+          <t>RF-00015245-PAR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1985,7 +1985,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RF-00015245-PAR</t>
+          <t>RF-00016198-PAR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RF-00016198-PAR</t>
+          <t>RF-00016551-PAR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2021,7 +2021,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RF-00016551-PAR</t>
+          <t>RF-00000004-MCG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RF-00000004-MCG</t>
+          <t>RF-00000234-MCG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2057,7 +2057,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RF-00000234-MCG</t>
+          <t>RF-00002792-MCG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RF-00002792-MCG</t>
+          <t>RF-00002793-MCG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>RF-00002793-MCG</t>
+          <t>RF-00002797-MCG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2111,7 +2111,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RF-00002797-MCG</t>
+          <t>RF-00011581-PAR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2129,7 +2129,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RF-00011581-PAR</t>
+          <t>RF-00011794-PAR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RF-00011794-PAR</t>
+          <t>RF-00011798-PAR</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2165,7 +2165,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RF-00011798-PAR</t>
+          <t>RF-00011792-PAR</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2183,7 +2183,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RF-00011792-PAR</t>
+          <t>RF-00011811-PAR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RF-00011811-PAR</t>
+          <t>RF-00011829-PAR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2219,7 +2219,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RF-00011829-PAR</t>
+          <t>RF-00011831-PAR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2237,7 +2237,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RF-00011831-PAR</t>
+          <t>RF-00012380-PAR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RF-00012380-PAR</t>
+          <t>RF-00012783-PAR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2273,7 +2273,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RF-00012783-PAR</t>
+          <t>RF-00012854-PAR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2291,7 +2291,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RF-00012854-PAR</t>
+          <t>RF-00013161-PAR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RF-00014483-PAR</t>
+          <t>RF-00014871-PAR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2381,7 +2381,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RF-00014871-PAR</t>
+          <t>RF-00015011-PAR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>RF-00014932-PAR</t>
+          <t>RF-00016554-PAR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RF-00015011-PAR</t>
+          <t>RF-00000235-MCG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RF-00015243-PAR</t>
+          <t>RF-00000304-MCG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2453,7 +2453,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RF-00015246-PAR</t>
+          <t>RF-00002526-MCG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RF-00016212-PAR</t>
+          <t>RF-00003072-PAR</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2489,7 +2489,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RF-00016554-PAR</t>
+          <t>RF-00011799-PAR</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RF-00000235-MCG</t>
+          <t>RF-00011830-PAR</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2525,7 +2525,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>RF-00000304-MCG</t>
+          <t>RF-00011989-PAR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RF-00002526-MCG</t>
+          <t>RF-00012379-PAR</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RF-00003072-PAR</t>
+          <t>RF-00012851-PAR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>RF-00011799-PAR</t>
+          <t>RF-00013067-PAR</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2597,7 +2597,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>RF-00011830-PAR</t>
+          <t>RF-00013429-PAR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2615,7 +2615,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>RF-00011989-PAR</t>
+          <t>RF-00013766-PAR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2633,7 +2633,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RF-00012379-PAR</t>
+          <t>RF-00013777-PAR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RF-00012851-PAR</t>
+          <t>RF-00014483-PAR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2669,7 +2669,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RF-00013067-PAR</t>
+          <t>RF-00014589-PAR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2687,7 +2687,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RF-00013429-PAR</t>
+          <t>RF-00014594-PAR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2705,7 +2705,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RF-00013766-PAR</t>
+          <t>RF-00014834-PAR</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2723,7 +2723,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RF-00013777-PAR</t>
+          <t>RF-00014864-PAR</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RF-00014589-PAR</t>
+          <t>RF-00014932-PAR</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2759,7 +2759,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RF-00014594-PAR</t>
+          <t>RF-00015019-PAR</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2777,7 +2777,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RF-00014834-PAR</t>
+          <t>RF-00015033-PAR</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2795,7 +2795,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RF-00014864-PAR</t>
+          <t>RF-00015020-PAR</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RF-00015019-PAR</t>
+          <t>RF-00015243-PAR</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RF-00015033-PAR</t>
+          <t>RF-00015246-PAR</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2849,7 +2849,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RF-00015020-PAR</t>
+          <t>RF-00016212-PAR</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
